--- a/api-test2/all_result/ALL_RESULT_SESSION.xlsx
+++ b/api-test2/all_result/ALL_RESULT_SESSION.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11116"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43997044-C97E-634C-B857-12EB4F0B38F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A68A8C-5B07-2A49-B05F-2E6A46AD2417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13380" yWindow="800" windowWidth="15420" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1586,10 +1586,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:Z80"/>
+  <dimension ref="A2:S80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>12</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>3.9849514404368733</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>12</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>6.5022288414133129</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>12</v>
       </c>
@@ -1726,7 +1726,7 @@
         <v>7.5056503779908041</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>12</v>
       </c>
@@ -1759,7 +1759,7 @@
         <v>-5.1045861297539261</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>12</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>3.0769422576853174</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:18">
       <c r="I7" t="s">
         <v>18</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>-3.6227987382330298</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>12</v>
       </c>
@@ -1852,7 +1852,7 @@
         <v>1.6601286605501144</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>12</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>2.0071221313637579</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>12</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>5.1434042232087904</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:18">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>17.693460430059801</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:18">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>5.5519410000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:18">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>-4.4288100000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:18">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>9.1245980000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:18">
       <c r="A15" s="1">
         <v>10</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>14.213108443578548</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:18">
       <c r="A16" s="1">
         <v>10</v>
       </c>
@@ -2176,72 +2176,8 @@
         <v>29</v>
       </c>
       <c r="J16" cm="1">
-        <f t="array" aca="1" ref="J16:Z16" ca="1">TRANSPOSE(_xlfn._xlws.FILTER(F:F, H:H=I16))</f>
-        <v>-11.82088744588745</v>
-      </c>
-      <c r="K16">
-        <f ca="1"/>
-        <v>2.5801265458728722</v>
-      </c>
-      <c r="L16">
-        <f ca="1"/>
-        <v>0.20485703094398389</v>
-      </c>
-      <c r="M16">
-        <f ca="1"/>
-        <v>1.260848</v>
-      </c>
-      <c r="N16">
-        <f ca="1"/>
-        <v>9.8310359999999992</v>
-      </c>
-      <c r="O16">
-        <f ca="1"/>
-        <v>-2.2282999999999999</v>
-      </c>
-      <c r="P16">
-        <f ca="1"/>
-        <v>4.2175929999999999</v>
-      </c>
-      <c r="Q16">
-        <f ca="1"/>
-        <v>8.5399290000000008</v>
-      </c>
-      <c r="R16">
-        <f ca="1"/>
-        <v>-0.39742</v>
-      </c>
-      <c r="S16">
-        <f ca="1"/>
-        <v>-4.0303399999999998</v>
-      </c>
-      <c r="T16">
-        <f ca="1"/>
-        <v>-0.77009000000000005</v>
-      </c>
-      <c r="U16">
-        <f ca="1"/>
-        <v>-2.3860700000000001</v>
-      </c>
-      <c r="V16">
-        <f ca="1"/>
-        <v>-5.1045861297539261</v>
-      </c>
-      <c r="W16">
-        <f ca="1"/>
-        <v>-3.6227987382330298</v>
-      </c>
-      <c r="X16">
-        <f ca="1"/>
-        <v>-18.011741606126051</v>
-      </c>
-      <c r="Y16">
-        <f ca="1"/>
-        <v>3.0769422576853174</v>
-      </c>
-      <c r="Z16">
-        <f ca="1"/>
-        <v>8.6928187633262297</v>
+        <f t="array" aca="1" ref="J16" ca="1">TRANSPOSE(_xlfn._xlws.FILTER(F:F, H:H=I16))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:19">
